--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/59.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/59.xlsx
@@ -426,13 +426,13 @@
         <v>-7.175496219893339</v>
       </c>
       <c r="E2">
-        <v>-18.89603802409783</v>
+        <v>-17.64988801819309</v>
       </c>
       <c r="F2">
-        <v>-5.786909571222534</v>
+        <v>-6.212816394914622</v>
       </c>
       <c r="G2">
-        <v>-10.88014879202956</v>
+        <v>-10.50548773225916</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.765697871499563</v>
       </c>
       <c r="E3">
-        <v>-19.99152569976737</v>
+        <v>-19.22269043969311</v>
       </c>
       <c r="F3">
-        <v>-5.901802684269919</v>
+        <v>-6.184523488735296</v>
       </c>
       <c r="G3">
-        <v>-10.34942530499238</v>
+        <v>-8.251956346585255</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.410666813598362</v>
       </c>
       <c r="E4">
-        <v>-19.40612080784781</v>
+        <v>-18.74032191687007</v>
       </c>
       <c r="F4">
-        <v>-5.411448532054938</v>
+        <v>-6.330161480645587</v>
       </c>
       <c r="G4">
-        <v>-10.38899294527775</v>
+        <v>-8.558459894793138</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.148837399560438</v>
       </c>
       <c r="E5">
-        <v>-20.79635327125459</v>
+        <v>-17.34426130741542</v>
       </c>
       <c r="F5">
-        <v>-5.443534413901741</v>
+        <v>-5.819662193259736</v>
       </c>
       <c r="G5">
-        <v>-10.71761755877904</v>
+        <v>-10.25089022756151</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.961143844030355</v>
       </c>
       <c r="E6">
-        <v>-21.00856662020204</v>
+        <v>-17.84484788117131</v>
       </c>
       <c r="F6">
-        <v>-5.761735773843665</v>
+        <v>-6.081113035427804</v>
       </c>
       <c r="G6">
-        <v>-11.14873004108509</v>
+        <v>-8.727228195839645</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.828035132619063</v>
       </c>
       <c r="E7">
-        <v>-21.63845018382494</v>
+        <v>-18.43919198078202</v>
       </c>
       <c r="F7">
-        <v>-5.403461111270419</v>
+        <v>-4.714637725585524</v>
       </c>
       <c r="G7">
-        <v>-9.919342402349042</v>
+        <v>-9.59320400854774</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.732638105153671</v>
       </c>
       <c r="E8">
-        <v>-22.32794657928481</v>
+        <v>-20.04264764283996</v>
       </c>
       <c r="F8">
-        <v>-5.026025982679228</v>
+        <v>-5.572490043625272</v>
       </c>
       <c r="G8">
-        <v>-10.5049514238818</v>
+        <v>-10.05119149954159</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.658608518381155</v>
       </c>
       <c r="E9">
-        <v>-22.84143930396257</v>
+        <v>-20.89216672430888</v>
       </c>
       <c r="F9">
-        <v>-5.093259841760337</v>
+        <v>-5.595034889184509</v>
       </c>
       <c r="G9">
-        <v>-10.54146674117996</v>
+        <v>-10.54432374198035</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.578857604960684</v>
       </c>
       <c r="E10">
-        <v>-22.03175720833913</v>
+        <v>-21.72488969568335</v>
       </c>
       <c r="F10">
-        <v>-4.883360210845739</v>
+        <v>-4.994241796809316</v>
       </c>
       <c r="G10">
-        <v>-10.6655923356294</v>
+        <v>-10.32567876183919</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.489839002736988</v>
       </c>
       <c r="E11">
-        <v>-23.66561704488457</v>
+        <v>-22.85120722239711</v>
       </c>
       <c r="F11">
-        <v>-4.726085543795278</v>
+        <v>-5.148870091275078</v>
       </c>
       <c r="G11">
-        <v>-11.24548735556137</v>
+        <v>-11.2696410958159</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.383812406128003</v>
       </c>
       <c r="E12">
-        <v>-24.27780333208549</v>
+        <v>-21.72248507598528</v>
       </c>
       <c r="F12">
-        <v>-4.721331258637129</v>
+        <v>-5.094339929194667</v>
       </c>
       <c r="G12">
-        <v>-10.73131328567501</v>
+        <v>-10.88901774352927</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.255104558703875</v>
       </c>
       <c r="E13">
-        <v>-24.12893880603135</v>
+        <v>-22.44277509469731</v>
       </c>
       <c r="F13">
-        <v>-4.917226969994454</v>
+        <v>-4.976514584644844</v>
       </c>
       <c r="G13">
-        <v>-9.892202550018096</v>
+        <v>-10.66374505121848</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.119952187398577</v>
       </c>
       <c r="E14">
-        <v>-25.67449339942722</v>
+        <v>-23.44557849285187</v>
       </c>
       <c r="F14">
-        <v>-4.588660254835978</v>
+        <v>-5.051206906734715</v>
       </c>
       <c r="G14">
-        <v>-9.446573325522342</v>
+        <v>-9.100032039562512</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.986093777561322</v>
       </c>
       <c r="E15">
-        <v>-25.57064190500931</v>
+        <v>-22.61547297945383</v>
       </c>
       <c r="F15">
-        <v>-4.102144213907064</v>
+        <v>-4.776154406311896</v>
       </c>
       <c r="G15">
-        <v>-9.454862931552677</v>
+        <v>-9.241746562462094</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.86543268781729</v>
       </c>
       <c r="E16">
-        <v>-26.5022033500752</v>
+        <v>-23.41166022253442</v>
       </c>
       <c r="F16">
-        <v>-4.533996269605712</v>
+        <v>-4.352850403291833</v>
       </c>
       <c r="G16">
-        <v>-8.359482865700784</v>
+        <v>-9.613640006161662</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.780007236480113</v>
       </c>
       <c r="E17">
-        <v>-27.26281490135153</v>
+        <v>-24.21797313349615</v>
       </c>
       <c r="F17">
-        <v>-4.244248561993531</v>
+        <v>-3.495376590965875</v>
       </c>
       <c r="G17">
-        <v>-8.81323616894991</v>
+        <v>-8.57544630395514</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.736644745123028</v>
       </c>
       <c r="E18">
-        <v>-26.30840277644294</v>
+        <v>-25.78765090793088</v>
       </c>
       <c r="F18">
-        <v>-4.357645864803783</v>
+        <v>-4.148272816106068</v>
       </c>
       <c r="G18">
-        <v>-9.092205909907674</v>
+        <v>-8.111748121906041</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.747125740955576</v>
       </c>
       <c r="E19">
-        <v>-27.77927830497831</v>
+        <v>-25.42032826727271</v>
       </c>
       <c r="F19">
-        <v>-3.859794448785112</v>
+        <v>-3.547366488757921</v>
       </c>
       <c r="G19">
-        <v>-8.541536385996384</v>
+        <v>-7.45193322211052</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.82248808843016</v>
       </c>
       <c r="E20">
-        <v>-29.08657629540862</v>
+        <v>-27.34856155668676</v>
       </c>
       <c r="F20">
-        <v>-3.407947314051083</v>
+        <v>-3.272841362404943</v>
       </c>
       <c r="G20">
-        <v>-8.079480234534765</v>
+        <v>-6.594319847434622</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.955092236682631</v>
       </c>
       <c r="E21">
-        <v>-29.58660133838757</v>
+        <v>-24.1559511534871</v>
       </c>
       <c r="F21">
-        <v>-3.422153947965533</v>
+        <v>-3.047430123901574</v>
       </c>
       <c r="G21">
-        <v>-8.152871718594868</v>
+        <v>-7.307894696242369</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.147867822080236</v>
       </c>
       <c r="E22">
-        <v>-29.85467567845663</v>
+        <v>-25.33972142993618</v>
       </c>
       <c r="F22">
-        <v>-3.236976758243902</v>
+        <v>-3.089836225346339</v>
       </c>
       <c r="G22">
-        <v>-7.017073202254013</v>
+        <v>-7.398666544383646</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.395595767428359</v>
       </c>
       <c r="E23">
-        <v>-30.83154450596926</v>
+        <v>-27.99730621455161</v>
       </c>
       <c r="F23">
-        <v>-2.926488046110167</v>
+        <v>-2.934638588603976</v>
       </c>
       <c r="G23">
-        <v>-7.895235133092167</v>
+        <v>-7.22017848163384</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.67874982879145</v>
       </c>
       <c r="E24">
-        <v>-31.09060944700007</v>
+        <v>-30.81254982174409</v>
       </c>
       <c r="F24">
-        <v>-2.829989677270611</v>
+        <v>-3.601266335883988</v>
       </c>
       <c r="G24">
-        <v>-8.12565572371652</v>
+        <v>-6.612451705353211</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.991578008162132</v>
       </c>
       <c r="E25">
-        <v>-31.36701165076924</v>
+        <v>-30.09919742521181</v>
       </c>
       <c r="F25">
-        <v>-2.441634896392465</v>
+        <v>-3.352607878247882</v>
       </c>
       <c r="G25">
-        <v>-8.278662517450556</v>
+        <v>-5.702210588239518</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.316691401192826</v>
       </c>
       <c r="E26">
-        <v>-30.6591160654162</v>
+        <v>-29.21545213719291</v>
       </c>
       <c r="F26">
-        <v>-2.626385277369885</v>
+        <v>-2.981703160999006</v>
       </c>
       <c r="G26">
-        <v>-8.49776766342168</v>
+        <v>-6.808025493631195</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.629173282330482</v>
       </c>
       <c r="E27">
-        <v>-31.48936648998248</v>
+        <v>-29.72437789583394</v>
       </c>
       <c r="F27">
-        <v>-2.864304625193395</v>
+        <v>-2.172620274772259</v>
       </c>
       <c r="G27">
-        <v>-8.038932672769771</v>
+        <v>-5.946535470128811</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.917792042188376</v>
       </c>
       <c r="E28">
-        <v>-30.95043279832963</v>
+        <v>-31.25000493935905</v>
       </c>
       <c r="F28">
-        <v>-2.721352202589211</v>
+        <v>-2.694457708733219</v>
       </c>
       <c r="G28">
-        <v>-8.033652352634634</v>
+        <v>-6.543847270142893</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.160526469859753</v>
       </c>
       <c r="E29">
-        <v>-30.93651226923005</v>
+        <v>-28.23863765136838</v>
       </c>
       <c r="F29">
-        <v>-2.664250893955084</v>
+        <v>-2.006161697118165</v>
       </c>
       <c r="G29">
-        <v>-8.25724659835701</v>
+        <v>-7.378449042775316</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.337104203057564</v>
       </c>
       <c r="E30">
-        <v>-31.50008085948463</v>
+        <v>-28.57131746586787</v>
       </c>
       <c r="F30">
-        <v>-2.522878218001551</v>
+        <v>-2.496766866720743</v>
       </c>
       <c r="G30">
-        <v>-8.110857585155978</v>
+        <v>-7.190946364522075</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.436803828860207</v>
       </c>
       <c r="E31">
-        <v>-29.67312236277812</v>
+        <v>-29.11189952205952</v>
       </c>
       <c r="F31">
-        <v>-2.600505939005689</v>
+        <v>-3.215638696592229</v>
       </c>
       <c r="G31">
-        <v>-8.432960423944907</v>
+        <v>-6.702044999282506</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.441590470846765</v>
       </c>
       <c r="E32">
-        <v>-30.86690735949516</v>
+        <v>-29.42732585058979</v>
       </c>
       <c r="F32">
-        <v>-2.380295590728622</v>
+        <v>-2.625970346420039</v>
       </c>
       <c r="G32">
-        <v>-8.910178873976388</v>
+        <v>-7.220264555817861</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.342927162394313</v>
       </c>
       <c r="E33">
-        <v>-30.37403504121133</v>
+        <v>-29.64820896302492</v>
       </c>
       <c r="F33">
-        <v>-2.883179232293603</v>
+        <v>-3.065791610285179</v>
       </c>
       <c r="G33">
-        <v>-8.350246443646217</v>
+        <v>-7.058322599673332</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.141486459144351</v>
       </c>
       <c r="E34">
-        <v>-30.55765786951135</v>
+        <v>-29.0207322833371</v>
       </c>
       <c r="F34">
-        <v>-2.939555995471416</v>
+        <v>-2.886772661015735</v>
       </c>
       <c r="G34">
-        <v>-8.78271624962337</v>
+        <v>-7.975889954065431</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.836986557559557</v>
       </c>
       <c r="E35">
-        <v>-29.81422961285713</v>
+        <v>-29.32807981423768</v>
       </c>
       <c r="F35">
-        <v>-2.96762718282258</v>
+        <v>-2.734974449020864</v>
       </c>
       <c r="G35">
-        <v>-8.370718857261069</v>
+        <v>-6.414987595572302</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.442809306070839</v>
       </c>
       <c r="E36">
-        <v>-28.30192760409958</v>
+        <v>-29.5115237678144</v>
       </c>
       <c r="F36">
-        <v>-2.651558282895795</v>
+        <v>-2.678095651067856</v>
       </c>
       <c r="G36">
-        <v>-8.399239207081891</v>
+        <v>-7.021784108556396</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.97468900662684</v>
       </c>
       <c r="E37">
-        <v>-29.77469150629616</v>
+        <v>-27.15142802618486</v>
       </c>
       <c r="F37">
-        <v>-3.136419351143074</v>
+        <v>-2.797724836655363</v>
       </c>
       <c r="G37">
-        <v>-7.901972093264583</v>
+        <v>-8.454045288484526</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.444411216933287</v>
       </c>
       <c r="E38">
-        <v>-29.14977115018566</v>
+        <v>-28.3933303234704</v>
       </c>
       <c r="F38">
-        <v>-2.876271107090456</v>
+        <v>-2.828090022025041</v>
       </c>
       <c r="G38">
-        <v>-7.599219393152694</v>
+        <v>-6.513228034450174</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.87276716875546</v>
       </c>
       <c r="E39">
-        <v>-28.41960000118889</v>
+        <v>-27.56105567102269</v>
       </c>
       <c r="F39">
-        <v>-2.65326155860785</v>
+        <v>-2.85878857748992</v>
       </c>
       <c r="G39">
-        <v>-7.474739570330558</v>
+        <v>-6.819771309204529</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.275212659570491</v>
       </c>
       <c r="E40">
-        <v>-28.36205215349942</v>
+        <v>-28.16043996220393</v>
       </c>
       <c r="F40">
-        <v>-2.397827215212537</v>
+        <v>-2.793394192829594</v>
       </c>
       <c r="G40">
-        <v>-8.929045673004694</v>
+        <v>-5.981905338670384</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.661707976659473</v>
       </c>
       <c r="E41">
-        <v>-27.69202819627253</v>
+        <v>-28.95486562889553</v>
       </c>
       <c r="F41">
-        <v>-2.691591992879231</v>
+        <v>-2.243350956514658</v>
       </c>
       <c r="G41">
-        <v>-8.532985246868448</v>
+        <v>-7.387817886651455</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.051328948138562</v>
       </c>
       <c r="E42">
-        <v>-26.94640136548758</v>
+        <v>-26.00633544623529</v>
       </c>
       <c r="F42">
-        <v>-2.739704186737324</v>
+        <v>-2.825671703092165</v>
       </c>
       <c r="G42">
-        <v>-8.852098663035415</v>
+        <v>-6.848894178313498</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.454242929308717</v>
       </c>
       <c r="E43">
-        <v>-26.42980210764056</v>
+        <v>-26.42960285478422</v>
       </c>
       <c r="F43">
-        <v>-2.796070655826687</v>
+        <v>-2.379463353270059</v>
       </c>
       <c r="G43">
-        <v>-7.477752166771295</v>
+        <v>-7.201218987330433</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.878449126588417</v>
       </c>
       <c r="E44">
-        <v>-27.27262357605214</v>
+        <v>-26.89978525405262</v>
       </c>
       <c r="F44">
-        <v>-2.648638721040682</v>
+        <v>-2.169520170442786</v>
       </c>
       <c r="G44">
-        <v>-7.983255917890309</v>
+        <v>-5.486369640170116</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.337242640275849</v>
       </c>
       <c r="E45">
-        <v>-26.34860656868303</v>
+        <v>-25.30639186123972</v>
       </c>
       <c r="F45">
-        <v>-3.061493432430676</v>
+        <v>-2.218143109458608</v>
       </c>
       <c r="G45">
-        <v>-8.965746380853055</v>
+        <v>-5.593383024727057</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.8357598636385002</v>
       </c>
       <c r="E46">
-        <v>-25.91481498654028</v>
+        <v>-27.86254788503135</v>
       </c>
       <c r="F46">
-        <v>-2.412054437303887</v>
+        <v>-2.230274296770874</v>
       </c>
       <c r="G46">
-        <v>-8.031020468930913</v>
+        <v>-6.820552597951797</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.3811271055035322</v>
       </c>
       <c r="E47">
-        <v>-25.69856223877798</v>
+        <v>-26.75437595366633</v>
       </c>
       <c r="F47">
-        <v>-2.650866995263705</v>
+        <v>-2.131398785352243</v>
       </c>
       <c r="G47">
-        <v>-8.476590103606963</v>
+        <v>-6.722891504543297</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.01845327491437036</v>
       </c>
       <c r="E48">
-        <v>-24.85204553557615</v>
+        <v>-26.20213760537894</v>
       </c>
       <c r="F48">
-        <v>-2.434425075212427</v>
+        <v>-2.552712070036599</v>
       </c>
       <c r="G48">
-        <v>-7.680754819239405</v>
+        <v>-5.596451900441961</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.3611480123089928</v>
       </c>
       <c r="E49">
-        <v>-24.40032119636301</v>
+        <v>-24.82118851368788</v>
       </c>
       <c r="F49">
-        <v>-2.579636654304986</v>
+        <v>-2.492512240778915</v>
       </c>
       <c r="G49">
-        <v>-8.92661242203333</v>
+        <v>-6.509616229266829</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.6431605593603237</v>
       </c>
       <c r="E50">
-        <v>-23.44844954537273</v>
+        <v>-24.60363156541138</v>
       </c>
       <c r="F50">
-        <v>-2.551726213104238</v>
+        <v>-2.539953735181819</v>
       </c>
       <c r="G50">
-        <v>-7.794793181430679</v>
+        <v>-5.697231527748455</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.8628281440274153</v>
       </c>
       <c r="E51">
-        <v>-23.43035376323808</v>
+        <v>-24.6150342629627</v>
       </c>
       <c r="F51">
-        <v>-2.925414293499499</v>
+        <v>-1.968935105869845</v>
       </c>
       <c r="G51">
-        <v>-8.582785783415703</v>
+        <v>-5.540828114291127</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.022879215592934</v>
       </c>
       <c r="E52">
-        <v>-23.30955219060946</v>
+        <v>-25.8469965598014</v>
       </c>
       <c r="F52">
-        <v>-2.713523944249194</v>
+        <v>-2.862252934179943</v>
       </c>
       <c r="G52">
-        <v>-8.739132917598864</v>
+        <v>-5.862421129067009</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.123105979772188</v>
       </c>
       <c r="E53">
-        <v>-23.92512577636813</v>
+        <v>-23.1808122030454</v>
       </c>
       <c r="F53">
-        <v>-2.823153610686616</v>
+        <v>-2.785610278255209</v>
       </c>
       <c r="G53">
-        <v>-8.398888289254728</v>
+        <v>-7.402331318295619</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.166426014239705</v>
       </c>
       <c r="E54">
-        <v>-24.44475005485227</v>
+        <v>-23.19213791653858</v>
       </c>
       <c r="F54">
-        <v>-2.434018062792159</v>
+        <v>-1.783826807355536</v>
       </c>
       <c r="G54">
-        <v>-8.256673873978716</v>
+        <v>-7.042263143262327</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.158051786849985</v>
       </c>
       <c r="E55">
-        <v>-22.98857395294579</v>
+        <v>-23.88525256273059</v>
       </c>
       <c r="F55">
-        <v>-3.167296073523439</v>
+        <v>-2.350069771479502</v>
       </c>
       <c r="G55">
-        <v>-8.033887401367922</v>
+        <v>-6.692017356844054</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.10118262309507</v>
       </c>
       <c r="E56">
-        <v>-22.11134061054992</v>
+        <v>-22.27939228097457</v>
       </c>
       <c r="F56">
-        <v>-2.875302670923165</v>
+        <v>-3.212206014020514</v>
       </c>
       <c r="G56">
-        <v>-9.181375454007945</v>
+        <v>-6.773218417831298</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.002016298837468</v>
       </c>
       <c r="E57">
-        <v>-23.05052800584473</v>
+        <v>-24.78752383791486</v>
       </c>
       <c r="F57">
-        <v>-3.05930791826737</v>
+        <v>-2.277361832901677</v>
       </c>
       <c r="G57">
-        <v>-8.955937234420194</v>
+        <v>-6.532866190589131</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.8675024799716359</v>
       </c>
       <c r="E58">
-        <v>-21.27772552979594</v>
+        <v>-23.49802275033469</v>
       </c>
       <c r="F58">
-        <v>-2.699629300400086</v>
+        <v>-2.92406655976546</v>
       </c>
       <c r="G58">
-        <v>-8.779087891712328</v>
+        <v>-7.610806302540143</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.7045344279918935</v>
       </c>
       <c r="E59">
-        <v>-21.96019373359591</v>
+        <v>-20.98803451905126</v>
       </c>
       <c r="F59">
-        <v>-2.71307733918104</v>
+        <v>-2.589553820747467</v>
       </c>
       <c r="G59">
-        <v>-8.631199201382005</v>
+        <v>-7.212206687975275</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.5213563503924812</v>
       </c>
       <c r="E60">
-        <v>-22.32360830118547</v>
+        <v>-19.75888440457132</v>
       </c>
       <c r="F60">
-        <v>-2.931034073940436</v>
+        <v>-3.13088192340974</v>
       </c>
       <c r="G60">
-        <v>-9.441826003219026</v>
+        <v>-8.344472852225728</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.3260004828915575</v>
       </c>
       <c r="E61">
-        <v>-22.19945565779117</v>
+        <v>-22.05599360122818</v>
       </c>
       <c r="F61">
-        <v>-3.305087198549206</v>
+        <v>-3.396583432254847</v>
       </c>
       <c r="G61">
-        <v>-8.772499906089179</v>
+        <v>-7.930545411814033</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.1270281421876126</v>
       </c>
       <c r="E62">
-        <v>-20.74085682229059</v>
+        <v>-19.27398446477799</v>
       </c>
       <c r="F62">
-        <v>-2.925670062004843</v>
+        <v>-2.758243840036415</v>
       </c>
       <c r="G62">
-        <v>-8.994167414307698</v>
+        <v>-6.998130260678304</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.06676698963045162</v>
       </c>
       <c r="E63">
-        <v>-21.1459831639648</v>
+        <v>-17.89661286755299</v>
       </c>
       <c r="F63">
-        <v>-2.963254570790052</v>
+        <v>-3.145526452009809</v>
       </c>
       <c r="G63">
-        <v>-9.19188643609513</v>
+        <v>-7.272789671343937</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.2464656769791491</v>
       </c>
       <c r="E64">
-        <v>-21.46668063624</v>
+        <v>-21.07995348445895</v>
       </c>
       <c r="F64">
-        <v>-3.238661029484972</v>
+        <v>-2.907900089780655</v>
       </c>
       <c r="G64">
-        <v>-9.413484422857326</v>
+        <v>-8.643292624236963</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.4038977542010748</v>
       </c>
       <c r="E65">
-        <v>-20.66649927908464</v>
+        <v>-20.29871020560368</v>
       </c>
       <c r="F65">
-        <v>-2.83459113480792</v>
+        <v>-3.152735481336889</v>
       </c>
       <c r="G65">
-        <v>-9.035946499013301</v>
+        <v>-8.498505915076937</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.5330594584021127</v>
       </c>
       <c r="E66">
-        <v>-19.91854934113376</v>
+        <v>-21.4154952945313</v>
       </c>
       <c r="F66">
-        <v>-3.185556202728456</v>
+        <v>-3.209862921118621</v>
       </c>
       <c r="G66">
-        <v>-9.399798627597979</v>
+        <v>-8.266572405141137</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.6288005133254674</v>
       </c>
       <c r="E67">
-        <v>-20.01298160961571</v>
+        <v>-19.66644013617874</v>
       </c>
       <c r="F67">
-        <v>-3.179059841063324</v>
+        <v>-3.547950084387761</v>
       </c>
       <c r="G67">
-        <v>-9.727817411265585</v>
+        <v>-8.565762958252771</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.687919434056532</v>
       </c>
       <c r="E68">
-        <v>-21.27741306508941</v>
+        <v>-21.5072421779267</v>
       </c>
       <c r="F68">
-        <v>-3.144101116685913</v>
+        <v>-3.522895064952551</v>
       </c>
       <c r="G68">
-        <v>-9.602513262604171</v>
+        <v>-8.273468271499439</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.7093690504872678</v>
       </c>
       <c r="E69">
-        <v>-19.92911427099366</v>
+        <v>-19.16998353071784</v>
       </c>
       <c r="F69">
-        <v>-3.168110098363975</v>
+        <v>-3.532756801687992</v>
       </c>
       <c r="G69">
-        <v>-9.394399127823428</v>
+        <v>-7.8257666454961</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.6925000345848743</v>
       </c>
       <c r="E70">
-        <v>-20.97341207648049</v>
+        <v>-18.43107242688626</v>
       </c>
       <c r="F70">
-        <v>-3.238100397590906</v>
+        <v>-3.046806935623849</v>
       </c>
       <c r="G70">
-        <v>-9.711208404295062</v>
+        <v>-7.198534134898085</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.6397136657915264</v>
       </c>
       <c r="E71">
-        <v>-21.05706657682419</v>
+        <v>-19.90842367325261</v>
       </c>
       <c r="F71">
-        <v>-3.199070757157859</v>
+        <v>-4.300055191041785</v>
       </c>
       <c r="G71">
-        <v>-9.418486657167165</v>
+        <v>-8.422095213485019</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.5552742426955395</v>
       </c>
       <c r="E72">
-        <v>-20.00659646126489</v>
+        <v>-20.50817929930248</v>
       </c>
       <c r="F72">
-        <v>-3.547385493228907</v>
+        <v>-3.080030710170895</v>
       </c>
       <c r="G72">
-        <v>-8.795826009958883</v>
+        <v>-8.375237751922175</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.4444293154298565</v>
       </c>
       <c r="E73">
-        <v>-20.46455198071259</v>
+        <v>-20.42321606997057</v>
       </c>
       <c r="F73">
-        <v>-3.517402772837807</v>
+        <v>-3.006875374671958</v>
       </c>
       <c r="G73">
-        <v>-9.640508393758386</v>
+        <v>-7.371136047679067</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.3145286181614578</v>
       </c>
       <c r="E74">
-        <v>-20.13670404797927</v>
+        <v>-18.61845162437565</v>
       </c>
       <c r="F74">
-        <v>-3.607241658302941</v>
+        <v>-3.822614576861298</v>
       </c>
       <c r="G74">
-        <v>-8.268552111373621</v>
+        <v>-7.181865538107854</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.172480169051996</v>
       </c>
       <c r="E75">
-        <v>-20.60542375014319</v>
+        <v>-18.88695390523844</v>
       </c>
       <c r="F75">
-        <v>-3.699338908403491</v>
+        <v>-4.237963625068109</v>
       </c>
       <c r="G75">
-        <v>-8.987235131948465</v>
+        <v>-8.030782109652087</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.02418813518887276</v>
       </c>
       <c r="E76">
-        <v>-21.90644527559887</v>
+        <v>-20.8198560513544</v>
       </c>
       <c r="F76">
-        <v>-4.06131785911295</v>
+        <v>-3.956699830044936</v>
       </c>
       <c r="G76">
-        <v>-8.956397400250154</v>
+        <v>-8.638277147744967</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.1248470186594676</v>
       </c>
       <c r="E77">
-        <v>-20.90367810523638</v>
+        <v>-20.78439809987434</v>
       </c>
       <c r="F77">
-        <v>-3.447296071226091</v>
+        <v>-3.827821801911262</v>
       </c>
       <c r="G77">
-        <v>-8.98793696760279</v>
+        <v>-7.900886234327703</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.2707473543223903</v>
       </c>
       <c r="E78">
-        <v>-20.4805057946416</v>
+        <v>-21.6889653113805</v>
       </c>
       <c r="F78">
-        <v>-3.481793145329151</v>
+        <v>-4.100762430495843</v>
       </c>
       <c r="G78">
-        <v>-8.749670384050363</v>
+        <v>-6.885836555986224</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.4105279321805264</v>
       </c>
       <c r="E79">
-        <v>-23.19907553871834</v>
+        <v>-23.08417456772172</v>
       </c>
       <c r="F79">
-        <v>-3.806535210701841</v>
+        <v>-3.92256621644947</v>
       </c>
       <c r="G79">
-        <v>-9.020876895718539</v>
+        <v>-6.010412446309049</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.5417938631616351</v>
       </c>
       <c r="E80">
-        <v>-22.4251185745414</v>
+        <v>-22.55150828409548</v>
       </c>
       <c r="F80">
-        <v>-4.253979642990948</v>
+        <v>-3.658812665880353</v>
       </c>
       <c r="G80">
-        <v>-8.721742621881072</v>
+        <v>-5.764736861839734</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.6625617595305066</v>
       </c>
       <c r="E81">
-        <v>-23.27638111850328</v>
+        <v>-23.90765039517252</v>
       </c>
       <c r="F81">
-        <v>-4.101584373865956</v>
+        <v>-4.15311658064844</v>
       </c>
       <c r="G81">
-        <v>-7.416440863383992</v>
+        <v>-6.824061776223425</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.7697900862649205</v>
       </c>
       <c r="E82">
-        <v>-22.6869504131909</v>
+        <v>-23.02135557628731</v>
       </c>
       <c r="F82">
-        <v>-4.204880008494579</v>
+        <v>-4.299436753881806</v>
       </c>
       <c r="G82">
-        <v>-9.243256171228001</v>
+        <v>-8.481678412100822</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.8597426543766824</v>
       </c>
       <c r="E83">
-        <v>-24.59963745133662</v>
+        <v>-25.72564251334385</v>
       </c>
       <c r="F83">
-        <v>-4.096170475194026</v>
+        <v>-3.958141794280944</v>
       </c>
       <c r="G83">
-        <v>-7.09044813358642</v>
+        <v>-7.421989337707811</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.9265942571077493</v>
       </c>
       <c r="E84">
-        <v>-25.04411170366347</v>
+        <v>-23.80904740212951</v>
       </c>
       <c r="F84">
-        <v>-4.024676447200386</v>
+        <v>-3.793826762583397</v>
       </c>
       <c r="G84">
-        <v>-9.21260051953435</v>
+        <v>-7.712598956781654</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.9643541635302629</v>
       </c>
       <c r="E85">
-        <v>-25.1698810122785</v>
+        <v>-25.74637386735097</v>
       </c>
       <c r="F85">
-        <v>-3.841284094045455</v>
+        <v>-3.472430275957073</v>
       </c>
       <c r="G85">
-        <v>-8.564591025131868</v>
+        <v>-7.551683269754299</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.9669930714567291</v>
       </c>
       <c r="E86">
-        <v>-27.10219898524747</v>
+        <v>-26.08936048869192</v>
       </c>
       <c r="F86">
-        <v>-4.268600416002285</v>
+        <v>-4.324507610376171</v>
       </c>
       <c r="G86">
-        <v>-8.878546611348652</v>
+        <v>-6.39546530852722</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.9261032166382204</v>
       </c>
       <c r="E87">
-        <v>-29.20138669692509</v>
+        <v>-28.62698599684417</v>
       </c>
       <c r="F87">
-        <v>-3.994662844543935</v>
+        <v>-4.520403321733495</v>
       </c>
       <c r="G87">
-        <v>-7.454800154547528</v>
+        <v>-7.710294817086321</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.835254234715784</v>
       </c>
       <c r="E88">
-        <v>-28.65592747422719</v>
+        <v>-29.09005869192052</v>
       </c>
       <c r="F88">
-        <v>-4.315831277518435</v>
+        <v>-3.928438597983919</v>
       </c>
       <c r="G88">
-        <v>-7.836641787592606</v>
+        <v>-7.415014018256567</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.6870533178996969</v>
       </c>
       <c r="E89">
-        <v>-30.17555655392914</v>
+        <v>-30.56809373786202</v>
       </c>
       <c r="F89">
-        <v>-4.384858683548779</v>
+        <v>-3.468376780666506</v>
       </c>
       <c r="G89">
-        <v>-8.041405650287608</v>
+        <v>-5.964624290955388</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.4716471183935287</v>
       </c>
       <c r="E90">
-        <v>-30.83574919408538</v>
+        <v>-30.36909221183195</v>
       </c>
       <c r="F90">
-        <v>-4.162899923941067</v>
+        <v>-4.212578402949529</v>
       </c>
       <c r="G90">
-        <v>-7.607846674828035</v>
+        <v>-6.630381619993903</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.1851817093939877</v>
       </c>
       <c r="E91">
-        <v>-32.20679224888466</v>
+        <v>-34.38170283868154</v>
       </c>
       <c r="F91">
-        <v>-4.216111650846876</v>
+        <v>-3.903540365434338</v>
       </c>
       <c r="G91">
-        <v>-8.082691463707858</v>
+        <v>-7.224935735573773</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.1786808949169515</v>
       </c>
       <c r="E92">
-        <v>-35.0321049180332</v>
+        <v>-34.06789543960901</v>
       </c>
       <c r="F92">
-        <v>-4.160301062533831</v>
+        <v>-3.585231313490163</v>
       </c>
       <c r="G92">
-        <v>-7.984374882282583</v>
+        <v>-7.296225023216438</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.6254657921910194</v>
       </c>
       <c r="E93">
-        <v>-34.77756392253605</v>
+        <v>-37.18807742953</v>
       </c>
       <c r="F93">
-        <v>-4.425270107393048</v>
+        <v>-3.992882759094981</v>
       </c>
       <c r="G93">
-        <v>-6.92251409001581</v>
+        <v>-6.9599000807908</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.150106350910572</v>
       </c>
       <c r="E94">
-        <v>-36.93590709017587</v>
+        <v>-39.4577621875964</v>
       </c>
       <c r="F94">
-        <v>-4.395707860922498</v>
+        <v>-3.593385815248761</v>
       </c>
       <c r="G94">
-        <v>-8.639869520149356</v>
+        <v>-7.403638983783631</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.751600377911209</v>
       </c>
       <c r="E95">
-        <v>-38.13741087083898</v>
+        <v>-40.09015452581955</v>
       </c>
       <c r="F95">
-        <v>-4.619559940952117</v>
+        <v>-3.794760357220548</v>
       </c>
       <c r="G95">
-        <v>-8.483764055790562</v>
+        <v>-7.581759575978579</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.428359411495155</v>
       </c>
       <c r="E96">
-        <v>-41.45788273764522</v>
+        <v>-42.45476289179774</v>
       </c>
       <c r="F96">
-        <v>-4.489494133381863</v>
+        <v>-3.387298956325584</v>
       </c>
       <c r="G96">
-        <v>-8.981868737629306</v>
+        <v>-6.010107876119435</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.156138028056454</v>
       </c>
       <c r="E97">
-        <v>-43.332820416463</v>
+        <v>-42.20710064831825</v>
       </c>
       <c r="F97">
-        <v>-4.499561751886312</v>
+        <v>-3.537375679990372</v>
       </c>
       <c r="G97">
-        <v>-8.777766984042158</v>
+        <v>-7.725314762197995</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.940615016582426</v>
       </c>
       <c r="E98">
-        <v>-45.06044910004827</v>
+        <v>-45.60718535241633</v>
       </c>
       <c r="F98">
-        <v>-4.809862794869067</v>
+        <v>-4.0358534516986</v>
       </c>
       <c r="G98">
-        <v>-9.584897849789709</v>
+        <v>-9.660153170988423</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.74016215578432</v>
       </c>
       <c r="E99">
-        <v>-46.43979511194061</v>
+        <v>-48.33978883744283</v>
       </c>
       <c r="F99">
-        <v>-5.06280042588869</v>
+        <v>-3.631788308139294</v>
       </c>
       <c r="G99">
-        <v>-9.425491771528263</v>
+        <v>-8.466317480798605</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.572861926434886</v>
       </c>
       <c r="E100">
-        <v>-48.86939840111389</v>
+        <v>-49.16082834587751</v>
       </c>
       <c r="F100">
-        <v>-4.545928701825591</v>
+        <v>-3.209041769601466</v>
       </c>
       <c r="G100">
-        <v>-9.664672065649528</v>
+        <v>-8.565961590985127</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.362724336706701</v>
       </c>
       <c r="E101">
-        <v>-50.7771822340278</v>
+        <v>-50.90975331060235</v>
       </c>
       <c r="F101">
-        <v>-4.742401673989093</v>
+        <v>-2.90385609672558</v>
       </c>
       <c r="G101">
-        <v>-10.10538513001947</v>
+        <v>-8.594726921175855</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.193971231633298</v>
       </c>
       <c r="E102">
-        <v>-52.88553331285994</v>
+        <v>-53.48625237175494</v>
       </c>
       <c r="F102">
-        <v>-4.271470882974019</v>
+        <v>-2.819929185442782</v>
       </c>
       <c r="G102">
-        <v>-10.30934121960288</v>
+        <v>-8.255197370668201</v>
       </c>
     </row>
   </sheetData>
